--- a/healthcare_surveys/014_mental_wellness_among_staff_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/014_mental_wellness_among_staff_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,7 +918,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>quite_good</t>
+          <t>quite good</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>quite_bad</t>
+          <t>quite bad</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>very_bad</t>
+          <t>very bad</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>work_life_balance</t>
+          <t>work life balance</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>lack_of_recognition</t>
+          <t>lack of recognition</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>lack_of_support</t>
+          <t>lack of support</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>lack_of_autonomy</t>
+          <t>lack of autonomy</t>
         </is>
       </c>
     </row>
